--- a/data/trans_orig/IP19C09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74939</t>
+          <t>74930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77745</t>
+          <t>77272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148778</t>
+          <t>148744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156397</t>
+          <t>156036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107177</t>
+          <t>106974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105480</t>
+          <t>104840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110951</t>
+          <t>110949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214120</t>
+          <t>214713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220343</t>
+          <t>220430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>491</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66377</t>
+          <t>66059</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73153</t>
+          <t>72753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77385</t>
+          <t>77378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140855</t>
+          <t>141169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146439</t>
+          <t>146442</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92625</t>
+          <t>91935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80052</t>
+          <t>80345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87613</t>
+          <t>87526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175062</t>
+          <t>175305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182927</t>
+          <t>183295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340926</t>
+          <t>341599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348698</t>
+          <t>348994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>344655</t>
+          <t>344290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>355122</t>
+          <t>354737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>689807</t>
+          <t>688969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702412</t>
+          <t>702151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69733</t>
+          <t>69359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67319</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139452</t>
+          <t>139497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146723</t>
+          <t>146714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104412</t>
+          <t>104238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110032</t>
+          <t>110112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105971</t>
+          <t>106068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111418</t>
+          <t>111419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213129</t>
+          <t>213669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220332</t>
+          <t>220821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75844</t>
+          <t>75811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146773</t>
+          <t>146970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85371</t>
+          <t>85373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91417</t>
+          <t>91302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179054</t>
+          <t>178828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185557</t>
+          <t>185536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335439</t>
+          <t>334722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343937</t>
+          <t>343778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>348197</t>
+          <t>348458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357450</t>
+          <t>357360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687756</t>
+          <t>687835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699842</t>
+          <t>699857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58034</t>
+          <t>58484</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64833</t>
+          <t>64831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69771</t>
+          <t>68302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130681</t>
+          <t>131204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137994</t>
+          <t>137982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95253</t>
+          <t>95463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101178</t>
+          <t>101122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99262</t>
+          <t>98612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104492</t>
+          <t>104430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197230</t>
+          <t>197454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205012</t>
+          <t>204918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70083</t>
+          <t>69836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69550</t>
+          <t>69711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142365</t>
+          <t>142215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99104</t>
+          <t>99132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105021</t>
+          <t>105015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94466</t>
+          <t>95312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102524</t>
+          <t>102852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>197313</t>
+          <t>197310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206903</t>
+          <t>206723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332222</t>
+          <t>332429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342418</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>340855</t>
+          <t>340852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>351497</t>
+          <t>351586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>677919</t>
+          <t>678274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>691793</t>
+          <t>692042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3807</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3010</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7441</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7571</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4916</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80925</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78381</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>72663</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68232</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>74930</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>68102</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>74927</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80925</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>77272</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148744</t>
+          <t>148752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156036</t>
+          <t>156221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7505</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>580</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3087</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2718</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6791</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108913</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>104126</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>110949</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>109481</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>106974</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>106842</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108913</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>104840</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>110949</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>339</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214713</t>
+          <t>213739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220430</t>
+          <t>220423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1774</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5223</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3149</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4174</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5116</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76095</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72646</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77383</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68576</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66059</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>65034</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76095</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77378</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,43%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>233</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141169</t>
+          <t>141290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146442</t>
+          <t>146444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2572</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9963</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>671</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4054</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5335</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2517</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9698</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1869,69 +1869,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>84708</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80080</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>87471</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>95318</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>91935</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>92613</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>84708</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>80345</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>87526</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,23%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>246</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175305</t>
+          <t>174952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183295</t>
+          <t>183312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7123</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18017</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4893</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9353</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6994</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17441</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>350641</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>343714</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>354608</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>515</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>346037</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>341599</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>348994</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>341577</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>348881</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,61%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>350641</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>344290</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>354737</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688969</t>
+          <t>689001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702151</t>
+          <t>701995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,67 +2674,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7377</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4559</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4342</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6499</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71742</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66271</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73648</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>72587</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>69359</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69576</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71742</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67149</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73648</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>195</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139497</t>
+          <t>139332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146714</t>
+          <t>146723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73648</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>73648</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>73648</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>73648</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>73648</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>73648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3017,102 +3017,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6461</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2603</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6730</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2648</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6021</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>9931</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>2,36%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>5251</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>9146</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3125,107 +3125,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>109441</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105628</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>111418</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>108123</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>104238</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>110112</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>103996</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>110055</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>109441</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>106068</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>111419</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>217564</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>212884</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>220255</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>97,64%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>217564</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>213669</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>220821</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112089</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112089</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112089</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110726</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110726</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110726</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112089</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112089</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,92 +3355,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78492</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75366</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>79146</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>71116</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78492</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75811</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79146</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>231</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146970</t>
+          <t>146966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79146</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79146</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79146</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>71116</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>71116</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>71116</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79146</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79146</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79146</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3703,67 +3703,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4132</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1714</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5321</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1369</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4302</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>94235</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>91472</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>95604</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>88980</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>85373</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>84483</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>90694</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>94235</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>91302</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>95604</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>243</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178828</t>
+          <t>178657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185536</t>
+          <t>185570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>95604</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>95604</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>95604</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>90694</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>90694</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>90694</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>95604</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>95604</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>95604</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12686</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2675</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11731</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3127</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>12029</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>353911</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>347801</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>357541</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>485</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>340805</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>334722</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>343778</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>336251</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>343974</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>353911</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>348458</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>357360</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687835</t>
+          <t>687569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699857</t>
+          <t>699531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>346453</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>346453</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>346453</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2592</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7070</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6695</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5218</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72672</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>69718</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73520</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>62962</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58484</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64831</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>58859</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>64832</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,79%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72672</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>68302</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73520</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>181</t>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131204</t>
+          <t>130176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137982</t>
+          <t>138292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73520</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>73520</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>73520</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>65554</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>65554</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>65554</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>73520</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>73520</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>73520</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5846</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3145</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6911</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6942</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2549</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102568</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>99271</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>104484</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>99229</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95463</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101122</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>95432</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>101193</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>102568</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>98612</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>104430</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197454</t>
+          <t>196692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204918</t>
+          <t>204436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>105117</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>105117</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>105117</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>102374</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>102374</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>102374</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>105117</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>105117</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>105117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5307,102 +5307,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>657</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3685</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3394</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4345</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1241</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4411</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72521</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70363</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73105</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72864</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>69836</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70184</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>73521</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72521</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69711</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73105</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>218</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142215</t>
+          <t>142281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73105</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73105</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73105</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>73521</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>73521</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>73521</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73105</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73105</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73105</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9462</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2448</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6602</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6170</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>7083</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>6,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4635</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9223</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>7083</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3547</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>12960</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -5763,102 +5763,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>99900</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95073</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>102542</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>103286</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>99132</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>105015</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>99564</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>105016</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>203187</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>197157</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>206999</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>93,76%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>99900</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95312</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>102852</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>203187</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>197310</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>206723</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>93,84%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>104535</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>104535</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>104535</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>105734</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>105734</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>105734</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>104535</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>104535</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>104535</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5993,67 +5993,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4364</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14639</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>8842</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4889</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14753</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4151</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14237</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4692</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>15426</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>347662</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>341639</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>351914</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>338340</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>332429</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>342293</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>332945</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>343031</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>347662</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>340852</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>351586</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>678274</t>
+          <t>678478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>692042</t>
+          <t>692081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>347182</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>347182</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>347182</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
